--- a/artfynd/A 34928-2025 artfynd.xlsx
+++ b/artfynd/A 34928-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75259095</v>
+        <v>75259102</v>
       </c>
       <c r="B2" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491072.396918871</v>
+        <v>491175</v>
       </c>
       <c r="R2" t="n">
-        <v>6255584.676596367</v>
+        <v>6255529</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2018-11-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-11-09</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,7 +759,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Hedbokskog med inslag av gran, asp, tall, ek</t>
+          <t>Hedbokskog, blockig brant</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Grov bok</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -789,6 +779,556 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Artinventering för Lst G</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>75259106</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>491170</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6255521</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Urshult</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2018-11-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2018-11-09</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Hedbokskog, blockig sluttning/brant</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Grov bok</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Artinventering för Lst G</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>75259095</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>491072</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6255585</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Urshult</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-11-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-11-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Hedbokskog med inslag av gran, asp, tall, ek</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Artinventering för Lst G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>75259108</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>491169</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6255518</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Urshult</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2018-11-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2018-11-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Hedbokskog, blockig sluttning</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Sten</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Artinventering för Lst G</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>75259109</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>491174</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6255479</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Urshult</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2018-11-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2018-11-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Hedbokskog, blockig sluttning</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Artinventering för Lst G</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>75259105</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tingsryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>491167</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6255526</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Urshult</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2018-11-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2018-11-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Hedbokskog, blockig brant</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Grov bokhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Artinventering för Lst G</t>
         </is>
